--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119565780</v>
+        <v>119565972</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119565972</v>
+        <v>119565780</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>100171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119566101</v>
+        <v>119566057</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119566057</v>
+        <v>119565880</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,210 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120361930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillvallen, Lillvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>445001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039944</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120362032</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillvallen, Lillvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>445001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039944</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120361930</v>
+        <v>120362032</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120362032</v>
+        <v>120361930</v>
       </c>
       <c r="B7" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,6 +1284,4486 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120398132</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445004</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039936</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120398133</v>
+      </c>
+      <c r="B9" t="n">
+        <v>74645</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>492</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039935</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>vid basen av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120398169</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445049</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039969</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>på marken i rikare stråk</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120398125</v>
+      </c>
+      <c r="B11" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039969</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120398114</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445036</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039990</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>på marken i rikare stråk</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120398134</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445009</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039922</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120398130</v>
+      </c>
+      <c r="B14" t="n">
+        <v>74645</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>492</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444995</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7039946</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120398167</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>445040</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039968</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>på marken i rikare stråk</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120398126</v>
+      </c>
+      <c r="B16" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>445003</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039966</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120398139</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96944</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039874</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>riklig vid källa</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120398113</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>445036</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039990</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>på marken i rikare stråk</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120398162</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74645</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>492</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>445065</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7039967</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120398136</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>444962</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7039895</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120398145</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97834</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>445016</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7039886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>på marken i rikare fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120398147</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>445021</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7039896</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120398141</v>
+      </c>
+      <c r="B23" t="n">
+        <v>102848</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>445010</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7039885</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>på marken i rikare fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120398159</v>
+      </c>
+      <c r="B24" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>445063</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7039966</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120398148</v>
+      </c>
+      <c r="B25" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>445023</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7039903</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120398149</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>445048</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7039922</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120398161</v>
+      </c>
+      <c r="B27" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>445065</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7039967</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120398163</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>445057</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7039979</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120398129</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78798</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>444994</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7039946</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>på grangrenar på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120398138</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>444999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7039878</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120398124</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>445000</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7039969</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120398151</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>445049</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7039945</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>på marken i rikare stråk</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120398127</v>
+      </c>
+      <c r="B33" t="n">
+        <v>74645</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>492</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>445003</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7039966</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120398146</v>
+      </c>
+      <c r="B34" t="n">
+        <v>74659</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>445008</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7039887</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120398123</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>445023</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7039976</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120398140</v>
+      </c>
+      <c r="B36" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>445007</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7039880</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>vid källa</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120398120</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74645</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>492</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>445030</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7039976</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120398131</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>444999</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7039943</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120398164</v>
+      </c>
+      <c r="B39" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>445051</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7039962</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120398144</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>445016</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7039886</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>på marken i rikare fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120398116</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96944</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>445036</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7039990</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>på marken</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120398158</v>
+      </c>
+      <c r="B42" t="n">
+        <v>74466</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>445062</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7039953</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120398128</v>
+      </c>
+      <c r="B43" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>444989</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7039942</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120362032</v>
+        <v>120361454</v>
       </c>
       <c r="B6" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120361930</v>
+        <v>120362032</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398132</v>
+        <v>120398162</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445004</v>
+        <v>445065</v>
       </c>
       <c r="R8" t="n">
-        <v>7039936</v>
+        <v>7039967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398133</v>
+        <v>120398167</v>
       </c>
       <c r="B9" t="n">
-        <v>74645</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>492</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445006</v>
+        <v>445040</v>
       </c>
       <c r="R9" t="n">
-        <v>7039935</v>
+        <v>7039968</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,19 +1511,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398169</v>
+        <v>120398145</v>
       </c>
       <c r="B10" t="n">
-        <v>91512</v>
+        <v>97834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445049</v>
+        <v>445016</v>
       </c>
       <c r="R10" t="n">
-        <v>7039969</v>
+        <v>7039886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,7 +1630,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1658,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398125</v>
+        <v>120398146</v>
       </c>
       <c r="B11" t="n">
-        <v>74654</v>
+        <v>74659</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445000</v>
+        <v>445008</v>
       </c>
       <c r="R11" t="n">
-        <v>7039969</v>
+        <v>7039887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,7 +1757,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398114</v>
+        <v>120398127</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>74645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1787,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>492</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445036</v>
+        <v>445003</v>
       </c>
       <c r="R12" t="n">
-        <v>7039990</v>
+        <v>7039966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,9 +1872,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398134</v>
+        <v>120398140</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445009</v>
+        <v>445007</v>
       </c>
       <c r="R13" t="n">
-        <v>7039922</v>
+        <v>7039880</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,19 +1999,9 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>vid källa</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398167</v>
+        <v>120398151</v>
       </c>
       <c r="B15" t="n">
         <v>100194</v>
@@ -2196,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445040</v>
+        <v>445049</v>
       </c>
       <c r="R15" t="n">
-        <v>7039968</v>
+        <v>7039945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398126</v>
+        <v>120398158</v>
       </c>
       <c r="B16" t="n">
-        <v>77479</v>
+        <v>74466</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445003</v>
+        <v>445062</v>
       </c>
       <c r="R16" t="n">
-        <v>7039966</v>
+        <v>7039953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2372,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2400,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120398139</v>
+        <v>120398159</v>
       </c>
       <c r="B17" t="n">
-        <v>96944</v>
+        <v>74654</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,25 +2402,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221063</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445001</v>
+        <v>445063</v>
       </c>
       <c r="R17" t="n">
-        <v>7039874</v>
+        <v>7039966</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,9 +2487,19 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120398113</v>
+        <v>120398139</v>
       </c>
       <c r="B18" t="n">
-        <v>91512</v>
+        <v>96944</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445036</v>
+        <v>445001</v>
       </c>
       <c r="R18" t="n">
-        <v>7039990</v>
+        <v>7039874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120398162</v>
+        <v>120398113</v>
       </c>
       <c r="B19" t="n">
-        <v>74645</v>
+        <v>91512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,25 +2646,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445065</v>
+        <v>445036</v>
       </c>
       <c r="R19" t="n">
-        <v>7039967</v>
+        <v>7039990</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,19 +2731,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2761,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398136</v>
+        <v>120398114</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,25 +2763,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444962</v>
+        <v>445036</v>
       </c>
       <c r="R20" t="n">
-        <v>7039895</v>
+        <v>7039990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2836,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,19 +2848,9 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2888,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120398145</v>
+        <v>120398164</v>
       </c>
       <c r="B21" t="n">
-        <v>97834</v>
+        <v>74654</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,25 +2880,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2928,10 +2908,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445016</v>
+        <v>445051</v>
       </c>
       <c r="R21" t="n">
-        <v>7039886</v>
+        <v>7039962</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,9 +2965,19 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3005,7 +2995,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398147</v>
+        <v>120398123</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -3038,26 +3028,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445021</v>
+        <v>445023</v>
       </c>
       <c r="R22" t="n">
-        <v>7039896</v>
+        <v>7039976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120398141</v>
+        <v>120398134</v>
       </c>
       <c r="B23" t="n">
-        <v>102848</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3153,25 +3134,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3162,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445010</v>
+        <v>445009</v>
       </c>
       <c r="R23" t="n">
-        <v>7039885</v>
+        <v>7039922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3197,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3226,7 +3207,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,9 +3219,19 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3258,7 +3249,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398159</v>
+        <v>120398148</v>
       </c>
       <c r="B24" t="n">
         <v>74654</v>
@@ -3298,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445063</v>
+        <v>445023</v>
       </c>
       <c r="R24" t="n">
-        <v>7039966</v>
+        <v>7039903</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3333,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3343,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,10 +3376,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398148</v>
+        <v>120398124</v>
       </c>
       <c r="B25" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3392,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,10 +3416,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445023</v>
+        <v>445000</v>
       </c>
       <c r="R25" t="n">
-        <v>7039903</v>
+        <v>7039969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3460,7 +3451,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3470,7 +3461,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,7 +3485,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3512,10 +3503,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398149</v>
+        <v>120398128</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3528,21 +3519,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3552,10 +3543,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445048</v>
+        <v>444989</v>
       </c>
       <c r="R26" t="n">
-        <v>7039922</v>
+        <v>7039942</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3587,7 +3578,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3597,7 +3588,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3621,7 +3612,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3639,10 +3630,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398161</v>
+        <v>120398120</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>74645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3651,25 +3642,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3679,10 +3670,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445065</v>
+        <v>445030</v>
       </c>
       <c r="R27" t="n">
-        <v>7039967</v>
+        <v>7039976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,7 +3705,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3724,7 +3715,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3738,17 +3729,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3766,10 +3757,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398163</v>
+        <v>120398144</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3778,25 +3769,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3806,10 +3797,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445057</v>
+        <v>445016</v>
       </c>
       <c r="R28" t="n">
-        <v>7039979</v>
+        <v>7039886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,7 +3832,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3851,7 +3842,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,19 +3854,9 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3893,10 +3874,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398129</v>
+        <v>120398141</v>
       </c>
       <c r="B29" t="n">
-        <v>78798</v>
+        <v>102848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3909,21 +3890,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>222002</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3933,10 +3914,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444994</v>
+        <v>445010</v>
       </c>
       <c r="R29" t="n">
-        <v>7039946</v>
+        <v>7039885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3968,7 +3949,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3978,7 +3959,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,19 +3971,9 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på grangrenar på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4020,10 +3991,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398138</v>
+        <v>120398161</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>74638</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4032,25 +4003,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4060,10 +4031,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444999</v>
+        <v>445065</v>
       </c>
       <c r="R30" t="n">
-        <v>7039878</v>
+        <v>7039967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4095,7 +4066,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4105,7 +4076,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4119,17 +4090,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4147,10 +4118,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398124</v>
+        <v>120398138</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4163,21 +4134,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4187,10 +4158,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445000</v>
+        <v>444999</v>
       </c>
       <c r="R31" t="n">
-        <v>7039969</v>
+        <v>7039878</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,7 +4193,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,7 +4203,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4256,7 +4227,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4274,10 +4245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120398151</v>
+        <v>120398136</v>
       </c>
       <c r="B32" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4286,25 +4257,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4314,10 +4285,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445049</v>
+        <v>444962</v>
       </c>
       <c r="R32" t="n">
-        <v>7039945</v>
+        <v>7039895</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4349,7 +4320,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4359,7 +4330,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4371,9 +4342,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4391,10 +4372,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120398127</v>
+        <v>120398129</v>
       </c>
       <c r="B33" t="n">
-        <v>74645</v>
+        <v>78798</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4403,25 +4384,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>492</v>
+        <v>6459</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4431,10 +4412,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445003</v>
+        <v>444994</v>
       </c>
       <c r="R33" t="n">
-        <v>7039966</v>
+        <v>7039946</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4466,7 +4447,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4476,7 +4457,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4500,7 +4481,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>på grangrenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4518,10 +4499,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120398146</v>
+        <v>120398169</v>
       </c>
       <c r="B34" t="n">
-        <v>74659</v>
+        <v>91512</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4530,25 +4511,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4558,10 +4539,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445008</v>
+        <v>445049</v>
       </c>
       <c r="R34" t="n">
-        <v>7039887</v>
+        <v>7039969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4593,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4603,7 +4584,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4615,19 +4596,9 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4645,10 +4616,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120398123</v>
+        <v>120398125</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4661,21 +4632,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4685,10 +4656,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445023</v>
+        <v>445000</v>
       </c>
       <c r="R35" t="n">
-        <v>7039976</v>
+        <v>7039969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4720,7 +4691,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4730,7 +4701,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4754,7 +4725,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4772,10 +4743,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120398140</v>
+        <v>120398163</v>
       </c>
       <c r="B36" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4784,25 +4755,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4812,10 +4783,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445007</v>
+        <v>445057</v>
       </c>
       <c r="R36" t="n">
-        <v>7039880</v>
+        <v>7039979</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4847,7 +4818,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4857,7 +4828,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4869,9 +4840,19 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>vid källa</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4889,7 +4870,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398120</v>
+        <v>120398133</v>
       </c>
       <c r="B37" t="n">
         <v>74645</v>
@@ -4929,10 +4910,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445030</v>
+        <v>445006</v>
       </c>
       <c r="R37" t="n">
-        <v>7039976</v>
+        <v>7039935</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4964,7 +4945,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4974,7 +4955,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,7 +4979,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5016,7 +4997,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398131</v>
+        <v>120398147</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -5051,7 +5032,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5065,10 +5046,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444999</v>
+        <v>445021</v>
       </c>
       <c r="R38" t="n">
-        <v>7039943</v>
+        <v>7039896</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5100,7 +5081,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5110,7 +5091,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5152,10 +5133,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398164</v>
+        <v>120398149</v>
       </c>
       <c r="B39" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5168,21 +5149,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5192,10 +5173,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445051</v>
+        <v>445048</v>
       </c>
       <c r="R39" t="n">
-        <v>7039962</v>
+        <v>7039922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5227,7 +5208,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5237,7 +5218,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5261,7 +5242,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5279,10 +5260,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398144</v>
+        <v>120398131</v>
       </c>
       <c r="B40" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5291,38 +5272,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445016</v>
+        <v>444999</v>
       </c>
       <c r="R40" t="n">
-        <v>7039886</v>
+        <v>7039943</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5354,7 +5344,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5364,7 +5354,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5376,9 +5366,19 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5513,10 +5513,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398158</v>
+        <v>120398126</v>
       </c>
       <c r="B42" t="n">
-        <v>74466</v>
+        <v>77479</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445062</v>
+        <v>445003</v>
       </c>
       <c r="R42" t="n">
-        <v>7039953</v>
+        <v>7039966</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398128</v>
+        <v>120398132</v>
       </c>
       <c r="B43" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5656,21 +5656,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444989</v>
+        <v>445004</v>
       </c>
       <c r="R43" t="n">
-        <v>7039942</v>
+        <v>7039936</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5764,6 +5764,112 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120443748</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilllvallen, Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>445008</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7039917</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120361454</v>
+        <v>120362032</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120362032</v>
+        <v>120361930</v>
       </c>
       <c r="B7" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398162</v>
+        <v>120398146</v>
       </c>
       <c r="B8" t="n">
-        <v>74645</v>
+        <v>74659</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445065</v>
+        <v>445008</v>
       </c>
       <c r="R8" t="n">
-        <v>7039967</v>
+        <v>7039887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398167</v>
+        <v>120398163</v>
       </c>
       <c r="B9" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445040</v>
+        <v>445057</v>
       </c>
       <c r="R9" t="n">
-        <v>7039968</v>
+        <v>7039979</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,9 +1511,19 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398145</v>
+        <v>120398148</v>
       </c>
       <c r="B10" t="n">
-        <v>97834</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445016</v>
+        <v>445023</v>
       </c>
       <c r="R10" t="n">
-        <v>7039886</v>
+        <v>7039903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,9 +1638,19 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1641,17 +1661,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398146</v>
+        <v>120398120</v>
       </c>
       <c r="B11" t="n">
-        <v>74659</v>
+        <v>74645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445008</v>
+        <v>445030</v>
       </c>
       <c r="R11" t="n">
-        <v>7039887</v>
+        <v>7039976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1768,17 +1788,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398127</v>
+        <v>120398161</v>
       </c>
       <c r="B12" t="n">
-        <v>74645</v>
+        <v>74638</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>492</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445003</v>
+        <v>445065</v>
       </c>
       <c r="R12" t="n">
-        <v>7039966</v>
+        <v>7039967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,17 +1894,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1902,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398140</v>
+        <v>120398132</v>
       </c>
       <c r="B13" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445007</v>
+        <v>445004</v>
       </c>
       <c r="R13" t="n">
-        <v>7039880</v>
+        <v>7039936</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,9 +2019,19 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>vid källa</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2012,17 +2042,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120398130</v>
+        <v>120398125</v>
       </c>
       <c r="B14" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444995</v>
+        <v>445000</v>
       </c>
       <c r="R14" t="n">
-        <v>7039946</v>
+        <v>7039969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,7 +2158,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2139,17 +2169,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398151</v>
+        <v>120398139</v>
       </c>
       <c r="B15" t="n">
-        <v>100194</v>
+        <v>96944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221063</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445049</v>
+        <v>445001</v>
       </c>
       <c r="R15" t="n">
-        <v>7039945</v>
+        <v>7039874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,7 +2275,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2256,17 +2286,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398158</v>
+        <v>120398144</v>
       </c>
       <c r="B16" t="n">
-        <v>74466</v>
+        <v>105017</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,21 +2309,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6428</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445062</v>
+        <v>445016</v>
       </c>
       <c r="R16" t="n">
-        <v>7039953</v>
+        <v>7039886</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,19 +2390,9 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2383,17 +2403,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120398159</v>
+        <v>120398136</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,21 +2426,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445063</v>
+        <v>444962</v>
       </c>
       <c r="R17" t="n">
-        <v>7039966</v>
+        <v>7039895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,7 +2519,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2510,17 +2530,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120398139</v>
+        <v>120398140</v>
       </c>
       <c r="B18" t="n">
-        <v>96944</v>
+        <v>105017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,21 +2553,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221063</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445001</v>
+        <v>445007</v>
       </c>
       <c r="R18" t="n">
-        <v>7039874</v>
+        <v>7039880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2602,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,7 +2636,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>vid källa</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2627,17 +2647,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120398113</v>
+        <v>120398130</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>74645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,25 +2666,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>492</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2674,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445036</v>
+        <v>444995</v>
       </c>
       <c r="R19" t="n">
-        <v>7039990</v>
+        <v>7039946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,9 +2751,19 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2744,17 +2774,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398114</v>
+        <v>120398147</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,38 +2793,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445036</v>
+        <v>445021</v>
       </c>
       <c r="R20" t="n">
-        <v>7039990</v>
+        <v>7039896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,9 +2887,19 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2861,17 +2910,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120398164</v>
+        <v>120398114</v>
       </c>
       <c r="B21" t="n">
-        <v>74654</v>
+        <v>100194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,25 +2929,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2908,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445051</v>
+        <v>445036</v>
       </c>
       <c r="R21" t="n">
-        <v>7039962</v>
+        <v>7039990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,19 +3014,9 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2988,17 +3027,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398123</v>
+        <v>120398151</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,25 +3046,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3035,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445023</v>
+        <v>445049</v>
       </c>
       <c r="R22" t="n">
-        <v>7039976</v>
+        <v>7039945</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,7 +3109,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3119,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,19 +3131,9 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3115,17 +3144,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120398134</v>
+        <v>120398145</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3134,25 +3163,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3162,10 +3191,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445009</v>
+        <v>445016</v>
       </c>
       <c r="R23" t="n">
-        <v>7039922</v>
+        <v>7039886</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3197,7 +3226,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3207,7 +3236,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,19 +3248,9 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3242,17 +3261,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398148</v>
+        <v>120398131</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3265,34 +3284,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445023</v>
+        <v>444999</v>
       </c>
       <c r="R24" t="n">
-        <v>7039903</v>
+        <v>7039943</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3352,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3362,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3358,7 +3386,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3369,17 +3397,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398124</v>
+        <v>120398138</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3392,21 +3420,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3416,10 +3444,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445000</v>
+        <v>444999</v>
       </c>
       <c r="R25" t="n">
-        <v>7039969</v>
+        <v>7039878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3451,7 +3479,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3461,7 +3489,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3485,7 +3513,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3496,17 +3524,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398128</v>
+        <v>120398124</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3519,21 +3547,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3543,10 +3571,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444989</v>
+        <v>445000</v>
       </c>
       <c r="R26" t="n">
-        <v>7039942</v>
+        <v>7039969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,7 +3606,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3588,7 +3616,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,7 +3640,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3623,17 +3651,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398120</v>
+        <v>120398169</v>
       </c>
       <c r="B27" t="n">
-        <v>74645</v>
+        <v>91512</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3642,25 +3670,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3670,10 +3698,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445030</v>
+        <v>445049</v>
       </c>
       <c r="R27" t="n">
-        <v>7039976</v>
+        <v>7039969</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3705,7 +3733,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3715,7 +3743,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3727,19 +3755,9 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3757,10 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398144</v>
+        <v>120398113</v>
       </c>
       <c r="B28" t="n">
-        <v>105017</v>
+        <v>91512</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,21 +3791,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3797,10 +3815,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445016</v>
+        <v>445036</v>
       </c>
       <c r="R28" t="n">
-        <v>7039886</v>
+        <v>7039990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3832,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3842,7 +3860,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,7 +3874,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3867,17 +3885,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398141</v>
+        <v>120398167</v>
       </c>
       <c r="B29" t="n">
-        <v>102848</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3890,21 +3908,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3914,10 +3932,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445010</v>
+        <v>445040</v>
       </c>
       <c r="R29" t="n">
-        <v>7039885</v>
+        <v>7039968</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3949,7 +3967,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3959,7 +3977,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3973,7 +3991,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3991,10 +4009,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398161</v>
+        <v>120398129</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>78798</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4007,21 +4025,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4031,10 +4049,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445065</v>
+        <v>444994</v>
       </c>
       <c r="R30" t="n">
-        <v>7039967</v>
+        <v>7039946</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4066,7 +4084,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4076,7 +4094,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4090,17 +4108,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på grangrenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4111,17 +4129,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398138</v>
+        <v>120398149</v>
       </c>
       <c r="B31" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4134,21 +4152,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4158,10 +4176,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444999</v>
+        <v>445048</v>
       </c>
       <c r="R31" t="n">
-        <v>7039878</v>
+        <v>7039922</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4193,7 +4211,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4203,7 +4221,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4227,7 +4245,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4238,17 +4256,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120398136</v>
+        <v>120398128</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4261,21 +4279,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4285,10 +4303,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444962</v>
+        <v>444989</v>
       </c>
       <c r="R32" t="n">
-        <v>7039895</v>
+        <v>7039942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4320,7 +4338,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4330,7 +4348,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4354,7 +4372,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4365,17 +4383,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120398129</v>
+        <v>120398158</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>74466</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4388,21 +4406,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4412,10 +4430,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444994</v>
+        <v>445062</v>
       </c>
       <c r="R33" t="n">
-        <v>7039946</v>
+        <v>7039953</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4447,7 +4465,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4457,7 +4475,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4481,7 +4499,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>på grangrenar på gammal gran # Picea abies</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4499,10 +4517,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120398169</v>
+        <v>120398127</v>
       </c>
       <c r="B34" t="n">
-        <v>91512</v>
+        <v>74645</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,25 +4529,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>492</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4539,10 +4557,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445049</v>
+        <v>445003</v>
       </c>
       <c r="R34" t="n">
-        <v>7039969</v>
+        <v>7039966</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4574,7 +4592,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,7 +4602,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4596,9 +4614,19 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4609,17 +4637,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120398125</v>
+        <v>120398116</v>
       </c>
       <c r="B35" t="n">
-        <v>74654</v>
+        <v>96944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4628,25 +4656,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>221063</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4656,10 +4684,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445000</v>
+        <v>445036</v>
       </c>
       <c r="R35" t="n">
-        <v>7039969</v>
+        <v>7039990</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4691,7 +4719,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4729,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4713,19 +4741,9 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4736,17 +4754,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120398163</v>
+        <v>120398164</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4759,21 +4777,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4783,10 +4801,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445057</v>
+        <v>445051</v>
       </c>
       <c r="R36" t="n">
-        <v>7039979</v>
+        <v>7039962</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4852,7 +4870,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4870,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398133</v>
+        <v>120398159</v>
       </c>
       <c r="B37" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4882,25 +4900,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4910,10 +4928,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445006</v>
+        <v>445063</v>
       </c>
       <c r="R37" t="n">
-        <v>7039935</v>
+        <v>7039966</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4945,7 +4963,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4955,7 +4973,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4979,7 +4997,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4997,10 +5015,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398147</v>
+        <v>120398162</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5009,47 +5027,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445021</v>
+        <v>445065</v>
       </c>
       <c r="R38" t="n">
-        <v>7039896</v>
+        <v>7039967</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5081,7 +5090,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5091,7 +5100,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5105,17 +5114,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5133,7 +5142,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398149</v>
+        <v>120398123</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -5173,10 +5182,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445048</v>
+        <v>445023</v>
       </c>
       <c r="R39" t="n">
-        <v>7039922</v>
+        <v>7039976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5208,7 +5217,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5218,7 +5227,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5253,14 +5262,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398131</v>
+        <v>120398134</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -5293,26 +5302,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444999</v>
+        <v>445009</v>
       </c>
       <c r="R40" t="n">
-        <v>7039943</v>
+        <v>7039922</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398116</v>
+        <v>120398141</v>
       </c>
       <c r="B41" t="n">
-        <v>96944</v>
+        <v>102848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221063</v>
+        <v>222002</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445036</v>
+        <v>445010</v>
       </c>
       <c r="R41" t="n">
-        <v>7039990</v>
+        <v>7039885</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>på marken</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5633,17 +5633,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398132</v>
+        <v>120398133</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5652,25 +5652,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445004</v>
+        <v>445006</v>
       </c>
       <c r="R43" t="n">
-        <v>7039936</v>
+        <v>7039935</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
+          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120362032</v>
+        <v>120361930</v>
       </c>
       <c r="B6" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120361930</v>
+        <v>120362032</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398146</v>
+        <v>120398164</v>
       </c>
       <c r="B8" t="n">
-        <v>74659</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445008</v>
+        <v>445051</v>
       </c>
       <c r="R8" t="n">
-        <v>7039887</v>
+        <v>7039962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398163</v>
+        <v>120398118</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445057</v>
+        <v>445030</v>
       </c>
       <c r="R9" t="n">
-        <v>7039979</v>
+        <v>7039976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>håligheter vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398148</v>
+        <v>120398167</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445023</v>
+        <v>445040</v>
       </c>
       <c r="R10" t="n">
-        <v>7039903</v>
+        <v>7039968</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,19 +1638,9 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1661,17 +1651,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398120</v>
+        <v>120398128</v>
       </c>
       <c r="B11" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1670,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445030</v>
+        <v>444989</v>
       </c>
       <c r="R11" t="n">
-        <v>7039976</v>
+        <v>7039942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,7 +1767,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>på jord vid bas av gran, trädet står på kalkklippa # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1788,17 +1778,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398161</v>
+        <v>120398131</v>
       </c>
       <c r="B12" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,38 +1797,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445065</v>
+        <v>444999</v>
       </c>
       <c r="R12" t="n">
-        <v>7039967</v>
+        <v>7039943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,17 +1893,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1922,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398132</v>
+        <v>120398138</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1937,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445004</v>
+        <v>444999</v>
       </c>
       <c r="R13" t="n">
-        <v>7039936</v>
+        <v>7039878</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2030,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2042,17 +2041,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120398125</v>
+        <v>120398127</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>74645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,25 +2060,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445000</v>
+        <v>445003</v>
       </c>
       <c r="R14" t="n">
-        <v>7039969</v>
+        <v>7039966</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,7 +2157,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2169,17 +2168,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398139</v>
+        <v>120398113</v>
       </c>
       <c r="B15" t="n">
-        <v>96944</v>
+        <v>91512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,21 +2191,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445001</v>
+        <v>445036</v>
       </c>
       <c r="R15" t="n">
-        <v>7039874</v>
+        <v>7039990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,7 +2274,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2286,17 +2285,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398144</v>
+        <v>120398126</v>
       </c>
       <c r="B16" t="n">
-        <v>105017</v>
+        <v>77479</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,25 +2304,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2333,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445016</v>
+        <v>445003</v>
       </c>
       <c r="R16" t="n">
-        <v>7039886</v>
+        <v>7039966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,9 +2389,19 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2403,17 +2412,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120398136</v>
+        <v>120398130</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,25 +2431,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2450,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444962</v>
+        <v>444995</v>
       </c>
       <c r="R17" t="n">
-        <v>7039895</v>
+        <v>7039946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2494,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2504,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,7 +2528,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2530,17 +2539,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120398140</v>
+        <v>120398169</v>
       </c>
       <c r="B18" t="n">
-        <v>105017</v>
+        <v>91512</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,21 +2562,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445007</v>
+        <v>445049</v>
       </c>
       <c r="R18" t="n">
-        <v>7039880</v>
+        <v>7039969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,7 +2645,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>vid källa</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2647,17 +2656,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120398130</v>
+        <v>120398129</v>
       </c>
       <c r="B19" t="n">
-        <v>74645</v>
+        <v>78798</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2666,25 +2675,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>6459</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,7 +2703,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444995</v>
+        <v>444994</v>
       </c>
       <c r="R19" t="n">
         <v>7039946</v>
@@ -2729,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,7 +2772,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
+          <t>på grangrenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2774,17 +2783,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398147</v>
+        <v>120398162</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,47 +2802,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445021</v>
+        <v>445065</v>
       </c>
       <c r="R20" t="n">
-        <v>7039896</v>
+        <v>7039967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2910,17 +2910,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120398114</v>
+        <v>120398134</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,25 +2929,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445036</v>
+        <v>445009</v>
       </c>
       <c r="R21" t="n">
-        <v>7039990</v>
+        <v>7039922</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,9 +3014,19 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3027,17 +3037,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398151</v>
+        <v>120398146</v>
       </c>
       <c r="B22" t="n">
-        <v>100194</v>
+        <v>74659</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3046,25 +3056,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3074,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445049</v>
+        <v>445008</v>
       </c>
       <c r="R22" t="n">
-        <v>7039945</v>
+        <v>7039887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,7 +3119,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3119,7 +3129,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,9 +3141,19 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3144,17 +3164,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120398145</v>
+        <v>120398116</v>
       </c>
       <c r="B23" t="n">
-        <v>97834</v>
+        <v>96944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,21 +3187,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220093</v>
+        <v>221063</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3191,10 +3211,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445016</v>
+        <v>445036</v>
       </c>
       <c r="R23" t="n">
-        <v>7039886</v>
+        <v>7039990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3226,7 +3246,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3236,7 +3256,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3250,7 +3270,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,17 +3281,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398131</v>
+        <v>120398161</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>74638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,47 +3300,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444999</v>
+        <v>445065</v>
       </c>
       <c r="R24" t="n">
-        <v>7039943</v>
+        <v>7039967</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3352,7 +3363,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3362,7 +3373,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,17 +3387,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3397,14 +3408,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398138</v>
+        <v>120398148</v>
       </c>
       <c r="B25" t="n">
         <v>74654</v>
@@ -3444,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444999</v>
+        <v>445023</v>
       </c>
       <c r="R25" t="n">
-        <v>7039878</v>
+        <v>7039903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3479,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3489,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,17 +3535,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398124</v>
+        <v>120398141</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>102848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3543,25 +3554,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3571,10 +3582,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445000</v>
+        <v>445010</v>
       </c>
       <c r="R26" t="n">
-        <v>7039969</v>
+        <v>7039885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3606,7 +3617,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3616,7 +3627,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3628,19 +3639,9 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3651,17 +3652,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398169</v>
+        <v>120398133</v>
       </c>
       <c r="B27" t="n">
-        <v>91512</v>
+        <v>74645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3670,25 +3671,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3698,10 +3699,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445049</v>
+        <v>445006</v>
       </c>
       <c r="R27" t="n">
-        <v>7039969</v>
+        <v>7039935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3733,7 +3734,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3743,7 +3744,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3755,9 +3756,19 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3775,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398113</v>
+        <v>120398158</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>74466</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3791,21 +3802,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>6428</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3815,10 +3826,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445036</v>
+        <v>445062</v>
       </c>
       <c r="R28" t="n">
-        <v>7039990</v>
+        <v>7039953</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3850,7 +3861,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,7 +3871,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3872,9 +3883,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3885,14 +3906,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398167</v>
+        <v>120398114</v>
       </c>
       <c r="B29" t="n">
         <v>100194</v>
@@ -3932,10 +3953,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445040</v>
+        <v>445036</v>
       </c>
       <c r="R29" t="n">
-        <v>7039968</v>
+        <v>7039990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,7 +3988,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3977,7 +3998,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4009,10 +4030,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398129</v>
+        <v>120398151</v>
       </c>
       <c r="B30" t="n">
-        <v>78798</v>
+        <v>100194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4025,21 +4046,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4049,10 +4070,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444994</v>
+        <v>445049</v>
       </c>
       <c r="R30" t="n">
-        <v>7039946</v>
+        <v>7039945</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4084,7 +4105,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4094,7 +4115,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4106,19 +4127,9 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på grangrenar på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4129,17 +4140,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398149</v>
+        <v>120398144</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4148,25 +4159,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4176,10 +4187,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445048</v>
+        <v>445016</v>
       </c>
       <c r="R31" t="n">
-        <v>7039922</v>
+        <v>7039886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4211,7 +4222,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4221,7 +4232,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4233,19 +4244,9 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4256,17 +4257,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120398128</v>
+        <v>120398145</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>97834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4275,25 +4276,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4303,10 +4304,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444989</v>
+        <v>445016</v>
       </c>
       <c r="R32" t="n">
-        <v>7039942</v>
+        <v>7039886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4338,7 +4339,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4348,7 +4349,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4360,19 +4361,9 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4383,17 +4374,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120398158</v>
+        <v>120398140</v>
       </c>
       <c r="B33" t="n">
-        <v>74466</v>
+        <v>105017</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,21 +4397,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4430,10 +4421,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445062</v>
+        <v>445007</v>
       </c>
       <c r="R33" t="n">
-        <v>7039953</v>
+        <v>7039880</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4465,7 +4456,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4475,7 +4466,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4487,19 +4478,9 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>vid källa</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4517,10 +4498,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120398127</v>
+        <v>120398136</v>
       </c>
       <c r="B34" t="n">
-        <v>74645</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4529,25 +4510,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4557,10 +4538,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445003</v>
+        <v>444962</v>
       </c>
       <c r="R34" t="n">
-        <v>7039966</v>
+        <v>7039895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4592,7 +4573,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4602,7 +4583,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4626,7 +4607,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4637,17 +4618,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120398116</v>
+        <v>120398147</v>
       </c>
       <c r="B35" t="n">
-        <v>96944</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4656,38 +4637,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445036</v>
+        <v>445021</v>
       </c>
       <c r="R35" t="n">
-        <v>7039990</v>
+        <v>7039896</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4719,7 +4709,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4729,7 +4719,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4741,9 +4731,19 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på marken</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4754,17 +4754,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120398164</v>
+        <v>120398132</v>
       </c>
       <c r="B36" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445051</v>
+        <v>445004</v>
       </c>
       <c r="R36" t="n">
-        <v>7039962</v>
+        <v>7039936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398159</v>
+        <v>120398163</v>
       </c>
       <c r="B37" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445063</v>
+        <v>445057</v>
       </c>
       <c r="R37" t="n">
-        <v>7039966</v>
+        <v>7039979</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398162</v>
+        <v>120398123</v>
       </c>
       <c r="B38" t="n">
-        <v>74645</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5027,25 +5027,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445065</v>
+        <v>445023</v>
       </c>
       <c r="R38" t="n">
-        <v>7039967</v>
+        <v>7039976</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398123</v>
+        <v>120398125</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445023</v>
+        <v>445000</v>
       </c>
       <c r="R39" t="n">
-        <v>7039976</v>
+        <v>7039969</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398134</v>
+        <v>120398149</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445009</v>
+        <v>445048</v>
       </c>
       <c r="R40" t="n">
         <v>7039922</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398141</v>
+        <v>120398124</v>
       </c>
       <c r="B41" t="n">
-        <v>102848</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5408,25 +5408,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445010</v>
+        <v>445000</v>
       </c>
       <c r="R41" t="n">
-        <v>7039885</v>
+        <v>7039969</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5493,9 +5493,19 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5506,17 +5516,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398126</v>
+        <v>120398139</v>
       </c>
       <c r="B42" t="n">
-        <v>77479</v>
+        <v>96944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5525,25 +5535,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>221063</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5553,10 +5563,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445003</v>
+        <v>445001</v>
       </c>
       <c r="R42" t="n">
-        <v>7039966</v>
+        <v>7039874</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,7 +5598,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5598,7 +5608,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5610,19 +5620,9 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5633,17 +5633,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398133</v>
+        <v>120398159</v>
       </c>
       <c r="B43" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5652,25 +5652,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445006</v>
+        <v>445063</v>
       </c>
       <c r="R43" t="n">
-        <v>7039935</v>
+        <v>7039966</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jana Novak, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Jana Novak</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398164</v>
+        <v>120398167</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
+        <v>100194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445051</v>
+        <v>445040</v>
       </c>
       <c r="R8" t="n">
-        <v>7039962</v>
+        <v>7039968</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,19 +1384,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398167</v>
+        <v>120398164</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445040</v>
+        <v>445051</v>
       </c>
       <c r="R10" t="n">
-        <v>7039968</v>
+        <v>7039962</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,9 +1628,19 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398128</v>
+        <v>120398126</v>
       </c>
       <c r="B11" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444989</v>
+        <v>445003</v>
       </c>
       <c r="R11" t="n">
-        <v>7039942</v>
+        <v>7039966</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398131</v>
+        <v>120398128</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,43 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444999</v>
+        <v>444989</v>
       </c>
       <c r="R12" t="n">
-        <v>7039943</v>
+        <v>7039942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,7 +1894,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1921,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398138</v>
+        <v>120398131</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,24 +1928,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
@@ -1964,7 +1964,7 @@
         <v>444999</v>
       </c>
       <c r="R13" t="n">
-        <v>7039878</v>
+        <v>7039943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120398127</v>
+        <v>120398138</v>
       </c>
       <c r="B14" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,25 +2060,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445003</v>
+        <v>444999</v>
       </c>
       <c r="R14" t="n">
-        <v>7039966</v>
+        <v>7039878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398113</v>
+        <v>120398127</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>74645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>492</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445036</v>
+        <v>445003</v>
       </c>
       <c r="R15" t="n">
-        <v>7039990</v>
+        <v>7039966</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,9 +2272,19 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2292,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398126</v>
+        <v>120398113</v>
       </c>
       <c r="B16" t="n">
-        <v>77479</v>
+        <v>91512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,25 +2314,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445003</v>
+        <v>445036</v>
       </c>
       <c r="R16" t="n">
-        <v>7039966</v>
+        <v>7039990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,19 +2399,9 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398133</v>
+        <v>120398144</v>
       </c>
       <c r="B27" t="n">
-        <v>74645</v>
+        <v>105017</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3671,25 +3671,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445006</v>
+        <v>445016</v>
       </c>
       <c r="R27" t="n">
-        <v>7039935</v>
+        <v>7039886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3756,19 +3756,9 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3786,10 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398158</v>
+        <v>120398133</v>
       </c>
       <c r="B28" t="n">
-        <v>74466</v>
+        <v>74645</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3798,25 +3788,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3826,10 +3816,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445062</v>
+        <v>445006</v>
       </c>
       <c r="R28" t="n">
-        <v>7039953</v>
+        <v>7039935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3861,7 +3851,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3871,7 +3861,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3895,7 +3885,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3913,10 +3903,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398114</v>
+        <v>120398158</v>
       </c>
       <c r="B29" t="n">
-        <v>100194</v>
+        <v>74466</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3929,21 +3919,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3953,10 +3943,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445036</v>
+        <v>445062</v>
       </c>
       <c r="R29" t="n">
-        <v>7039990</v>
+        <v>7039953</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3988,7 +3978,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3998,7 +3988,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4010,9 +4000,19 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398151</v>
+        <v>120398114</v>
       </c>
       <c r="B30" t="n">
         <v>100194</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445049</v>
+        <v>445036</v>
       </c>
       <c r="R30" t="n">
-        <v>7039945</v>
+        <v>7039990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398144</v>
+        <v>120398151</v>
       </c>
       <c r="B31" t="n">
-        <v>105017</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4163,21 +4163,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445016</v>
+        <v>445049</v>
       </c>
       <c r="R31" t="n">
-        <v>7039886</v>
+        <v>7039945</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120361930</v>
+        <v>120362032</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120362032</v>
+        <v>120361930</v>
       </c>
       <c r="B7" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398167</v>
+        <v>120398124</v>
       </c>
       <c r="B8" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445040</v>
+        <v>445000</v>
       </c>
       <c r="R8" t="n">
-        <v>7039968</v>
+        <v>7039969</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,9 +1384,19 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398118</v>
+        <v>120398139</v>
       </c>
       <c r="B9" t="n">
-        <v>74645</v>
+        <v>96944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>492</v>
+        <v>221063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445030</v>
+        <v>445001</v>
       </c>
       <c r="R9" t="n">
-        <v>7039976</v>
+        <v>7039874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,19 +1511,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>håligheter vid basen av gammal gran # Picea abies</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398164</v>
+        <v>120398159</v>
       </c>
       <c r="B10" t="n">
         <v>74654</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445051</v>
+        <v>445063</v>
       </c>
       <c r="R10" t="n">
-        <v>7039962</v>
+        <v>7039966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398126</v>
+        <v>120398144</v>
       </c>
       <c r="B11" t="n">
-        <v>77479</v>
+        <v>105017</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,25 +1670,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445003</v>
+        <v>445016</v>
       </c>
       <c r="R11" t="n">
-        <v>7039966</v>
+        <v>7039886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,19 +1755,9 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398128</v>
+        <v>120398151</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1787,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444989</v>
+        <v>445049</v>
       </c>
       <c r="R12" t="n">
-        <v>7039942</v>
+        <v>7039945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,19 +1872,9 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1912,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398131</v>
+        <v>120398146</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,43 +1908,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444999</v>
+        <v>445008</v>
       </c>
       <c r="R13" t="n">
-        <v>7039943</v>
+        <v>7039887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2048,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120398138</v>
+        <v>120398140</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2088,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444999</v>
+        <v>445007</v>
       </c>
       <c r="R14" t="n">
-        <v>7039878</v>
+        <v>7039880</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,19 +2116,9 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>vid källa</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2175,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398127</v>
+        <v>120398133</v>
       </c>
       <c r="B15" t="n">
         <v>74645</v>
@@ -2215,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445003</v>
+        <v>445006</v>
       </c>
       <c r="R15" t="n">
-        <v>7039966</v>
+        <v>7039935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,7 +2245,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398113</v>
+        <v>120398149</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445036</v>
+        <v>445048</v>
       </c>
       <c r="R16" t="n">
-        <v>7039990</v>
+        <v>7039922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,9 +2360,19 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2419,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120398130</v>
+        <v>120398136</v>
       </c>
       <c r="B17" t="n">
-        <v>74645</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,25 +2402,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2459,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444995</v>
+        <v>444962</v>
       </c>
       <c r="R17" t="n">
-        <v>7039946</v>
+        <v>7039895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,7 +2499,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2546,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120398169</v>
+        <v>120398163</v>
       </c>
       <c r="B18" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,25 +2529,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2586,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445049</v>
+        <v>445057</v>
       </c>
       <c r="R18" t="n">
-        <v>7039969</v>
+        <v>7039979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2602,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,9 +2614,19 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2663,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120398129</v>
+        <v>120398141</v>
       </c>
       <c r="B19" t="n">
-        <v>78798</v>
+        <v>102848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6459</v>
+        <v>222002</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2703,10 +2684,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444994</v>
+        <v>445010</v>
       </c>
       <c r="R19" t="n">
-        <v>7039946</v>
+        <v>7039885</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,19 +2741,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>på grangrenar på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2790,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398162</v>
+        <v>120398132</v>
       </c>
       <c r="B20" t="n">
-        <v>74645</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2802,25 +2773,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2830,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445065</v>
+        <v>445004</v>
       </c>
       <c r="R20" t="n">
-        <v>7039967</v>
+        <v>7039936</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,17 +2860,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3044,10 +3015,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398146</v>
+        <v>120398148</v>
       </c>
       <c r="B22" t="n">
-        <v>74659</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3031,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445008</v>
+        <v>445023</v>
       </c>
       <c r="R22" t="n">
-        <v>7039887</v>
+        <v>7039903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3119,7 +3090,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3100,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,7 +3124,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3171,10 +3142,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120398116</v>
+        <v>120398138</v>
       </c>
       <c r="B23" t="n">
-        <v>96944</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3183,25 +3154,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221063</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3211,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445036</v>
+        <v>444999</v>
       </c>
       <c r="R23" t="n">
-        <v>7039990</v>
+        <v>7039878</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3256,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3268,9 +3239,19 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>på marken</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3288,10 +3269,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398161</v>
+        <v>120398123</v>
       </c>
       <c r="B24" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3300,25 +3281,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3328,10 +3309,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445065</v>
+        <v>445023</v>
       </c>
       <c r="R24" t="n">
-        <v>7039967</v>
+        <v>7039976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3363,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3373,7 +3354,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3387,17 +3368,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3415,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398148</v>
+        <v>120398145</v>
       </c>
       <c r="B25" t="n">
-        <v>74654</v>
+        <v>97834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,25 +3408,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3455,10 +3436,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445023</v>
+        <v>445016</v>
       </c>
       <c r="R25" t="n">
-        <v>7039903</v>
+        <v>7039886</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3481,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,19 +3493,9 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3542,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398141</v>
+        <v>120398127</v>
       </c>
       <c r="B26" t="n">
-        <v>102848</v>
+        <v>74645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3554,25 +3525,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222002</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3582,10 +3553,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445010</v>
+        <v>445003</v>
       </c>
       <c r="R26" t="n">
-        <v>7039885</v>
+        <v>7039966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3617,7 +3588,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3627,7 +3598,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3639,9 +3610,19 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3659,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398144</v>
+        <v>120398113</v>
       </c>
       <c r="B27" t="n">
-        <v>105017</v>
+        <v>91512</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3675,21 +3656,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3699,10 +3680,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445016</v>
+        <v>445036</v>
       </c>
       <c r="R27" t="n">
-        <v>7039886</v>
+        <v>7039990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3744,7 +3725,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3758,7 +3739,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3776,10 +3757,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398133</v>
+        <v>120398167</v>
       </c>
       <c r="B28" t="n">
-        <v>74645</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3788,25 +3769,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3816,10 +3797,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445006</v>
+        <v>445040</v>
       </c>
       <c r="R28" t="n">
-        <v>7039935</v>
+        <v>7039968</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3851,7 +3832,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3861,7 +3842,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,19 +3854,9 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3903,10 +3874,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398158</v>
+        <v>120398131</v>
       </c>
       <c r="B29" t="n">
-        <v>74466</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3915,38 +3886,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445062</v>
+        <v>444999</v>
       </c>
       <c r="R29" t="n">
-        <v>7039953</v>
+        <v>7039943</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3978,7 +3958,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3988,7 +3968,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4012,7 +3992,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4030,10 +4010,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398114</v>
+        <v>120398129</v>
       </c>
       <c r="B30" t="n">
-        <v>100194</v>
+        <v>78798</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4046,21 +4026,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4070,10 +4050,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445036</v>
+        <v>444994</v>
       </c>
       <c r="R30" t="n">
-        <v>7039990</v>
+        <v>7039946</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4105,7 +4085,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4115,7 +4095,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4127,9 +4107,19 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på grangrenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4147,10 +4137,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398151</v>
+        <v>120398126</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>77479</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4159,25 +4149,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4187,10 +4177,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445049</v>
+        <v>445003</v>
       </c>
       <c r="R31" t="n">
-        <v>7039945</v>
+        <v>7039966</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,7 +4212,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,7 +4222,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4244,9 +4234,19 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120398145</v>
+        <v>120398162</v>
       </c>
       <c r="B32" t="n">
-        <v>97834</v>
+        <v>74645</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220093</v>
+        <v>492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445016</v>
+        <v>445065</v>
       </c>
       <c r="R32" t="n">
-        <v>7039886</v>
+        <v>7039967</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4361,9 +4361,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4381,10 +4391,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120398140</v>
+        <v>120398164</v>
       </c>
       <c r="B33" t="n">
-        <v>105017</v>
+        <v>74654</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,25 +4403,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4421,10 +4431,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445007</v>
+        <v>445051</v>
       </c>
       <c r="R33" t="n">
-        <v>7039880</v>
+        <v>7039962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4456,7 +4466,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4466,7 +4476,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4478,9 +4488,19 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>vid källa</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4498,10 +4518,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120398136</v>
+        <v>120398116</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>96944</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4510,25 +4530,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4538,10 +4558,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444962</v>
+        <v>445036</v>
       </c>
       <c r="R34" t="n">
-        <v>7039895</v>
+        <v>7039990</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4573,7 +4593,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4583,7 +4603,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4595,19 +4615,9 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4625,10 +4635,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120398147</v>
+        <v>120398128</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4641,43 +4651,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445021</v>
+        <v>444989</v>
       </c>
       <c r="R35" t="n">
-        <v>7039896</v>
+        <v>7039942</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4709,7 +4710,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4719,7 +4720,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4743,7 +4744,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4761,10 +4762,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120398132</v>
+        <v>120398125</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4777,21 +4778,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4801,10 +4802,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445004</v>
+        <v>445000</v>
       </c>
       <c r="R36" t="n">
-        <v>7039936</v>
+        <v>7039969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4836,7 +4837,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4846,7 +4847,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4870,7 +4871,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4888,10 +4889,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398163</v>
+        <v>120398130</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,25 +4901,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4928,10 +4929,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445057</v>
+        <v>444995</v>
       </c>
       <c r="R37" t="n">
-        <v>7039979</v>
+        <v>7039946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4963,7 +4964,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4973,7 +4974,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4997,7 +4998,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5015,10 +5016,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398123</v>
+        <v>120398114</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5027,25 +5028,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5055,10 +5056,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445023</v>
+        <v>445036</v>
       </c>
       <c r="R38" t="n">
-        <v>7039976</v>
+        <v>7039990</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5090,7 +5091,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5100,7 +5101,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,19 +5113,9 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5142,10 +5133,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398125</v>
+        <v>120398169</v>
       </c>
       <c r="B39" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5154,25 +5145,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5182,7 +5173,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445000</v>
+        <v>445049</v>
       </c>
       <c r="R39" t="n">
         <v>7039969</v>
@@ -5217,7 +5208,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5227,7 +5218,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5239,19 +5230,9 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5269,10 +5250,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398149</v>
+        <v>120398118</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5281,25 +5262,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5309,10 +5290,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445048</v>
+        <v>445030</v>
       </c>
       <c r="R40" t="n">
-        <v>7039922</v>
+        <v>7039976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5344,7 +5325,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5354,7 +5335,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5378,7 +5359,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>håligheter vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5396,7 +5377,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398124</v>
+        <v>120398147</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5429,17 +5410,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445000</v>
+        <v>445021</v>
       </c>
       <c r="R41" t="n">
-        <v>7039969</v>
+        <v>7039896</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5471,7 +5461,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5481,7 +5471,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5513,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398139</v>
+        <v>120398158</v>
       </c>
       <c r="B42" t="n">
-        <v>96944</v>
+        <v>74466</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5539,21 +5529,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221063</v>
+        <v>6428</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5563,10 +5553,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445001</v>
+        <v>445062</v>
       </c>
       <c r="R42" t="n">
-        <v>7039874</v>
+        <v>7039953</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5598,7 +5588,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5608,7 +5598,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5620,9 +5610,19 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398159</v>
+        <v>120398161</v>
       </c>
       <c r="B43" t="n">
-        <v>74654</v>
+        <v>74638</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5652,25 +5652,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445063</v>
+        <v>445065</v>
       </c>
       <c r="R43" t="n">
-        <v>7039966</v>
+        <v>7039967</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120362032</v>
+        <v>120361454</v>
       </c>
       <c r="B6" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120361930</v>
+        <v>120362032</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398124</v>
+        <v>120398164</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445000</v>
+        <v>445051</v>
       </c>
       <c r="R8" t="n">
-        <v>7039969</v>
+        <v>7039962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398139</v>
+        <v>120398134</v>
       </c>
       <c r="B9" t="n">
-        <v>96944</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445001</v>
+        <v>445009</v>
       </c>
       <c r="R9" t="n">
-        <v>7039874</v>
+        <v>7039922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,9 +1511,19 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398159</v>
+        <v>120398140</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445063</v>
+        <v>445007</v>
       </c>
       <c r="R10" t="n">
-        <v>7039966</v>
+        <v>7039880</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,19 +1638,9 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>vid källa</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398144</v>
+        <v>120398162</v>
       </c>
       <c r="B11" t="n">
-        <v>105017</v>
+        <v>74645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,25 +1670,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445016</v>
+        <v>445065</v>
       </c>
       <c r="R11" t="n">
-        <v>7039886</v>
+        <v>7039967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,9 +1755,19 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1775,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120398151</v>
+        <v>120398126</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>77479</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445049</v>
+        <v>445003</v>
       </c>
       <c r="R12" t="n">
-        <v>7039945</v>
+        <v>7039966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,9 +1882,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1892,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398146</v>
+        <v>120398132</v>
       </c>
       <c r="B13" t="n">
-        <v>74659</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445008</v>
+        <v>445004</v>
       </c>
       <c r="R13" t="n">
-        <v>7039887</v>
+        <v>7039936</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2021,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2019,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120398140</v>
+        <v>120398161</v>
       </c>
       <c r="B14" t="n">
-        <v>105017</v>
+        <v>74638</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445007</v>
+        <v>445065</v>
       </c>
       <c r="R14" t="n">
-        <v>7039880</v>
+        <v>7039967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,9 +2136,19 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>vid källa</t>
+          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2136,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398133</v>
+        <v>120398159</v>
       </c>
       <c r="B15" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2178,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445006</v>
+        <v>445063</v>
       </c>
       <c r="R15" t="n">
-        <v>7039935</v>
+        <v>7039966</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,7 +2275,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2263,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120398149</v>
+        <v>120398141</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>102848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,25 +2305,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445048</v>
+        <v>445010</v>
       </c>
       <c r="R16" t="n">
-        <v>7039922</v>
+        <v>7039885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,19 +2390,9 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2390,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120398136</v>
+        <v>120398144</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,25 +2422,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444962</v>
+        <v>445016</v>
       </c>
       <c r="R17" t="n">
-        <v>7039895</v>
+        <v>7039886</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,19 +2507,9 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare fuktstråk</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2644,10 +2654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120398141</v>
+        <v>120398145</v>
       </c>
       <c r="B19" t="n">
-        <v>102848</v>
+        <v>97834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222002</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445010</v>
+        <v>445016</v>
       </c>
       <c r="R19" t="n">
-        <v>7039885</v>
+        <v>7039886</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,10 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398132</v>
+        <v>120398148</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,21 +2787,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445004</v>
+        <v>445023</v>
       </c>
       <c r="R20" t="n">
-        <v>7039936</v>
+        <v>7039903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,7 +2880,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2888,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120398134</v>
+        <v>120398130</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,25 +2910,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2928,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445009</v>
+        <v>444995</v>
       </c>
       <c r="R21" t="n">
-        <v>7039922</v>
+        <v>7039946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2973,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +2983,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,7 +3007,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3015,7 +3025,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398148</v>
+        <v>120398125</v>
       </c>
       <c r="B22" t="n">
         <v>74654</v>
@@ -3055,10 +3065,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445023</v>
+        <v>445000</v>
       </c>
       <c r="R22" t="n">
-        <v>7039903</v>
+        <v>7039969</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3100,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,10 +3152,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120398138</v>
+        <v>120398124</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3158,21 +3168,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3182,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444999</v>
+        <v>445000</v>
       </c>
       <c r="R23" t="n">
-        <v>7039878</v>
+        <v>7039969</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,7 +3227,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3237,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,7 +3261,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3269,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398123</v>
+        <v>120398167</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3309,10 +3319,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445023</v>
+        <v>445040</v>
       </c>
       <c r="R24" t="n">
-        <v>7039976</v>
+        <v>7039968</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,7 +3364,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,19 +3376,9 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398145</v>
+        <v>120398151</v>
       </c>
       <c r="B25" t="n">
-        <v>97834</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445016</v>
+        <v>445049</v>
       </c>
       <c r="R25" t="n">
-        <v>7039886</v>
+        <v>7039945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>på marken i rikare fuktstråk</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398113</v>
+        <v>120398139</v>
       </c>
       <c r="B27" t="n">
-        <v>91512</v>
+        <v>96944</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445036</v>
+        <v>445001</v>
       </c>
       <c r="R27" t="n">
-        <v>7039990</v>
+        <v>7039874</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398167</v>
+        <v>120398114</v>
       </c>
       <c r="B28" t="n">
         <v>100194</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445040</v>
+        <v>445036</v>
       </c>
       <c r="R28" t="n">
-        <v>7039968</v>
+        <v>7039990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398131</v>
+        <v>120398136</v>
       </c>
       <c r="B29" t="n">
         <v>78542</v>
@@ -3907,26 +3907,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444999</v>
+        <v>444962</v>
       </c>
       <c r="R29" t="n">
-        <v>7039943</v>
+        <v>7039895</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3958,7 +3949,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3968,7 +3959,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4010,10 +4001,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398129</v>
+        <v>120398147</v>
       </c>
       <c r="B30" t="n">
-        <v>78798</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4022,38 +4013,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444994</v>
+        <v>445021</v>
       </c>
       <c r="R30" t="n">
-        <v>7039946</v>
+        <v>7039896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på grangrenar på gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398126</v>
+        <v>120398158</v>
       </c>
       <c r="B31" t="n">
-        <v>77479</v>
+        <v>74466</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4149,25 +4149,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445003</v>
+        <v>445062</v>
       </c>
       <c r="R31" t="n">
-        <v>7039966</v>
+        <v>7039953</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på bark vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120398162</v>
+        <v>120398169</v>
       </c>
       <c r="B32" t="n">
-        <v>74645</v>
+        <v>91512</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>492</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445065</v>
+        <v>445049</v>
       </c>
       <c r="R32" t="n">
-        <v>7039967</v>
+        <v>7039969</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4361,19 +4361,9 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4391,10 +4381,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120398164</v>
+        <v>120398113</v>
       </c>
       <c r="B33" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4403,25 +4393,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4431,10 +4421,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445051</v>
+        <v>445036</v>
       </c>
       <c r="R33" t="n">
-        <v>7039962</v>
+        <v>7039990</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4466,7 +4456,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4476,7 +4466,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4488,19 +4478,9 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4518,10 +4498,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120398116</v>
+        <v>120398131</v>
       </c>
       <c r="B34" t="n">
-        <v>96944</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4530,38 +4510,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445036</v>
+        <v>444999</v>
       </c>
       <c r="R34" t="n">
-        <v>7039990</v>
+        <v>7039943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4593,7 +4582,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4603,7 +4592,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4615,9 +4604,19 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>på marken</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4635,10 +4634,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120398128</v>
+        <v>120398116</v>
       </c>
       <c r="B35" t="n">
-        <v>74654</v>
+        <v>96944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4647,25 +4646,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>221063</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4675,10 +4674,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444989</v>
+        <v>445036</v>
       </c>
       <c r="R35" t="n">
-        <v>7039942</v>
+        <v>7039990</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4710,7 +4709,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4720,7 +4719,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4732,19 +4731,9 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>på marken</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4762,10 +4751,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120398125</v>
+        <v>120398118</v>
       </c>
       <c r="B36" t="n">
-        <v>74654</v>
+        <v>74645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4774,25 +4763,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4802,10 +4791,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445000</v>
+        <v>445030</v>
       </c>
       <c r="R36" t="n">
-        <v>7039969</v>
+        <v>7039976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4837,7 +4826,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4847,7 +4836,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4871,7 +4860,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>håligheter vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4889,10 +4878,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120398130</v>
+        <v>120398128</v>
       </c>
       <c r="B37" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4901,25 +4890,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4929,10 +4918,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444995</v>
+        <v>444989</v>
       </c>
       <c r="R37" t="n">
-        <v>7039946</v>
+        <v>7039942</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4964,7 +4953,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4974,7 +4963,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,7 +4987,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gran, kalkstenar i håligheten under granen # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5016,10 +5005,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120398114</v>
+        <v>120398129</v>
       </c>
       <c r="B38" t="n">
-        <v>100194</v>
+        <v>78798</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5032,21 +5021,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5056,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445036</v>
+        <v>444994</v>
       </c>
       <c r="R38" t="n">
-        <v>7039990</v>
+        <v>7039946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5091,7 +5080,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5101,7 +5090,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5113,9 +5102,19 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på grangrenar på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5133,10 +5132,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120398169</v>
+        <v>120398149</v>
       </c>
       <c r="B39" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5145,25 +5144,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5173,10 +5172,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445049</v>
+        <v>445048</v>
       </c>
       <c r="R39" t="n">
-        <v>7039969</v>
+        <v>7039922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5208,7 +5207,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5218,7 +5217,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5230,9 +5229,19 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5250,10 +5259,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120398118</v>
+        <v>120398138</v>
       </c>
       <c r="B40" t="n">
-        <v>74645</v>
+        <v>74654</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5262,25 +5271,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5290,10 +5299,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445030</v>
+        <v>444999</v>
       </c>
       <c r="R40" t="n">
-        <v>7039976</v>
+        <v>7039878</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5325,7 +5334,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5335,7 +5344,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5359,7 +5368,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>håligheter vid basen av gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5377,7 +5386,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398147</v>
+        <v>120398123</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5410,26 +5419,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445021</v>
+        <v>445023</v>
       </c>
       <c r="R41" t="n">
-        <v>7039896</v>
+        <v>7039976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398158</v>
+        <v>120398133</v>
       </c>
       <c r="B42" t="n">
-        <v>74466</v>
+        <v>74645</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445062</v>
+        <v>445006</v>
       </c>
       <c r="R42" t="n">
-        <v>7039953</v>
+        <v>7039935</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på bark vid basen av gammal gran # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120398161</v>
+        <v>120398146</v>
       </c>
       <c r="B43" t="n">
-        <v>74638</v>
+        <v>74659</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5652,25 +5652,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445065</v>
+        <v>445008</v>
       </c>
       <c r="R43" t="n">
-        <v>7039967</v>
+        <v>7039887</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av senvuxen glasbjörk (14 cm dbh) # Betula pubescens</t>
+          <t>riklig i rothåla på gammal grov gran (42 cm dbh) # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 35855-2024 artfynd.xlsx
+++ b/artfynd/A 35855-2024 artfynd.xlsx
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398167</v>
+        <v>120398127</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>74645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,25 +3291,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445040</v>
+        <v>445003</v>
       </c>
       <c r="R24" t="n">
-        <v>7039968</v>
+        <v>7039966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,9 +3376,19 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3396,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398151</v>
+        <v>120398167</v>
       </c>
       <c r="B25" t="n">
         <v>100194</v>
@@ -3436,10 +3446,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445049</v>
+        <v>445040</v>
       </c>
       <c r="R25" t="n">
-        <v>7039945</v>
+        <v>7039968</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3481,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3481,7 +3491,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,10 +3523,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398127</v>
+        <v>120398151</v>
       </c>
       <c r="B26" t="n">
-        <v>74645</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,25 +3535,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3553,10 +3563,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445003</v>
+        <v>445049</v>
       </c>
       <c r="R26" t="n">
-        <v>7039966</v>
+        <v>7039945</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3588,7 +3598,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3598,7 +3608,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3610,19 +3620,9 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>i hålighet vid basen av gammal grov gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120398139</v>
+        <v>120398136</v>
       </c>
       <c r="B27" t="n">
-        <v>96944</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,25 +3652,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445001</v>
+        <v>444962</v>
       </c>
       <c r="R27" t="n">
-        <v>7039874</v>
+        <v>7039895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,9 +3737,19 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>riklig vid källa</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3757,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398114</v>
+        <v>120398147</v>
       </c>
       <c r="B28" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3769,38 +3779,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445036</v>
+        <v>445021</v>
       </c>
       <c r="R28" t="n">
-        <v>7039990</v>
+        <v>7039896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3832,7 +3851,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3842,7 +3861,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3854,9 +3873,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>på marken i rikare stråk</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3874,10 +3903,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120398136</v>
+        <v>120398114</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3886,25 +3915,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3914,10 +3943,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444962</v>
+        <v>445036</v>
       </c>
       <c r="R29" t="n">
-        <v>7039895</v>
+        <v>7039990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3949,7 +3978,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3959,7 +3988,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,19 +4000,9 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på marken i rikare stråk</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4001,10 +4020,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398147</v>
+        <v>120398139</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>96944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4013,47 +4032,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillvallen, Kaxås, S. om Hällsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445021</v>
+        <v>445001</v>
       </c>
       <c r="R30" t="n">
-        <v>7039896</v>
+        <v>7039874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4085,7 +4095,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4095,7 +4105,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,19 +4117,9 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>riklig vid källa</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120398123</v>
+        <v>120398133</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>74645</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445023</v>
+        <v>445006</v>
       </c>
       <c r="R41" t="n">
-        <v>7039976</v>
+        <v>7039935</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5513,10 +5513,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120398133</v>
+        <v>120398123</v>
       </c>
       <c r="B42" t="n">
-        <v>74645</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445006</v>
+        <v>445023</v>
       </c>
       <c r="R42" t="n">
-        <v>7039935</v>
+        <v>7039976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>vid basen av gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
